--- a/results/3erall.xlsx
+++ b/results/3erall.xlsx
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>570</v>
+        <v>640</v>
       </c>
       <c r="C2" t="n">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="D2" t="n">
-        <v>17.36842105263158</v>
+        <v>18.4375</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>320</v>
+        <v>259</v>
       </c>
       <c r="C3" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>23.75</v>
+        <v>19.3050193050193</v>
       </c>
     </row>
     <row r="4">

--- a/results/3erall.xlsx
+++ b/results/3erall.xlsx
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C4" t="n">
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>17.72151898734177</v>
+        <v>17.28395061728395</v>
       </c>
     </row>
   </sheetData>
